--- a/Assignment 1 - Test cases.xlsx
+++ b/Assignment 1 - Test cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\3 year\Itpm\It23636910\test_automation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\3 year\Itpm\test_automation\test_automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E49927A-1E24-447C-90AE-5CE42233F899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DA84992-8518-44B6-BB55-F7991BC59DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="307">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -52,6 +52,9 @@
     <t>office eke වැඩ ගොඩක් තිබුනු නිසා lunch එක ගොඩාක් late උනා</t>
   </si>
   <si>
+    <t>office එකේ වැඩ ගොඩක් තිබුනු නිසා lunch එක ගොඩාක් late උනා</t>
+  </si>
+  <si>
     <t>FAIL</t>
   </si>
   <si>
@@ -67,6 +70,9 @@
     <t>මට පොත දෙන්න</t>
   </si>
   <si>
+    <t>මට book එක දෙන්න</t>
+  </si>
+  <si>
     <t>Neg_0003</t>
   </si>
   <si>
@@ -76,6 +82,9 @@
     <t>mama ada dinner ganna hotel ekata giya</t>
   </si>
   <si>
+    <t>මම අද රාත්‍රී ආහාරය ගන්න hotel එකට ගියා</t>
+  </si>
+  <si>
     <t>මම අද dinner ගන්න hotel එකට ගියා</t>
   </si>
   <si>
@@ -85,6 +94,9 @@
     <t>api meeting eka start karanne 10ta</t>
   </si>
   <si>
+    <t>අපි රැස්වීම එක start කරන්නේ 10ට</t>
+  </si>
+  <si>
     <t>අපි meeting එක start කරන්නේ 10ට</t>
   </si>
   <si>
@@ -94,6 +106,9 @@
     <t>mama file eka upload karala submit kala</t>
   </si>
   <si>
+    <t>මම file එක උඩු ගත කරලා submit කළා</t>
+  </si>
+  <si>
     <t>මම file එක upload කරලා submit කළා</t>
   </si>
   <si>
@@ -103,6 +118,9 @@
     <t>oya call ekak denna puluwanda</t>
   </si>
   <si>
+    <t>ඔයා කෝල් එකක් දෙන්න පුළුවන්ද</t>
+  </si>
+  <si>
     <t>ඔයා call එකක් දෙන්න පුළුවන්ද</t>
   </si>
   <si>
@@ -115,6 +133,9 @@
     <t>ඔෆිස් එකේ meeting එකක් තිබුණා</t>
   </si>
   <si>
+    <t>office එකේ meeting එකක් තිබුණා</t>
+  </si>
+  <si>
     <t>Neg_0008</t>
   </si>
   <si>
@@ -124,12 +145,18 @@
     <t>මට අද leave එකක් ඕන</t>
   </si>
   <si>
+    <t>මට today leave එකක් ඕන</t>
+  </si>
+  <si>
     <t>Neg_0009</t>
   </si>
   <si>
     <t>api game eka play kala</t>
   </si>
   <si>
+    <t>අපි game එක සෙල්ලම් කළා</t>
+  </si>
+  <si>
     <t>අපි game එක play කළා</t>
   </si>
   <si>
@@ -142,6 +169,9 @@
     <t>හරියට plan එක තිබ්බා</t>
   </si>
   <si>
+    <t>හරියට ප්ලෑන් එක තිබ්බ</t>
+  </si>
+  <si>
     <t>Neg_0011</t>
   </si>
   <si>
@@ -151,6 +181,9 @@
     <t>ඔෆිස් එකේ වැඩ ගොඩක් තිබුනා නිසා lunch එක late උනා</t>
   </si>
   <si>
+    <t>office එකේ වැඩ ගොඩක් තිබුන නිසා lunch එක late උනා</t>
+  </si>
+  <si>
     <t>Neg_0012</t>
   </si>
   <si>
@@ -160,6 +193,9 @@
     <t>මම උදේ wake up වෙලා zoom meeting එකට join උනා</t>
   </si>
   <si>
+    <t>මම morning wak up වෙලා zoom meeting එකට join වුණා</t>
+  </si>
+  <si>
     <t>Neg_0013</t>
   </si>
   <si>
@@ -169,349 +205,742 @@
     <t>exam එක නිසා මම රෑ whole night study කළා</t>
   </si>
   <si>
+    <t>exam එක නිසා මම ratri whole night study කළා</t>
+  </si>
+  <si>
     <t>Neg_0014</t>
   </si>
   <si>
     <t>project deadline eka nisa team eka pressure wela inne</t>
   </si>
   <si>
+    <t>ව්‍යාපෘතිය deadline එක නිසා team එක pressure වෙලා ඉන්නේ</t>
+  </si>
+  <si>
+    <t>Neg_0015</t>
+  </si>
+  <si>
+    <t>mama phone eka use karala assignment eka complete kala</t>
+  </si>
+  <si>
+    <t>මම phone එක use කරලා assignment එක සම්පූර්ණ කළා</t>
+  </si>
+  <si>
+    <t>මම phone එක use කරලා assignment එක complete කළා</t>
+  </si>
+  <si>
+    <t>Neg_0016</t>
+  </si>
+  <si>
+    <t>oyage WiFi password mokakda</t>
+  </si>
+  <si>
+    <t>ඔයාගේ WiFi මුරපදය මොකක්ද</t>
+  </si>
+  <si>
+    <t>ඔයාගේ WiFi password මොකක්ද</t>
+  </si>
+  <si>
+    <t>Neg_0017</t>
+  </si>
+  <si>
+    <t>mama bus eke travel karanawa</t>
+  </si>
+  <si>
+    <t>මම බස් එකේ travel කරනවා</t>
+  </si>
+  <si>
+    <t>මම bus එකේ travel කරනවා</t>
+  </si>
+  <si>
+    <t>Neg_0018</t>
+  </si>
+  <si>
+    <t>oyata update ekak thiyenawa</t>
+  </si>
+  <si>
+    <t>ඔයාට යාවත්කාලීන එකක් තියෙනවා</t>
+  </si>
+  <si>
+    <t>ඔයාට update එකක් තියෙනවා</t>
+  </si>
+  <si>
+    <t>Neg_0019</t>
+  </si>
+  <si>
+    <t>online class eka nisa mama home office eke inna wenawa</t>
+  </si>
+  <si>
+    <t>online class එක නිසා මම ගෙදර office එකේ ඉන්න වෙනවා</t>
+  </si>
+  <si>
+    <t>online class එක නිසා මම home office එකේ ඉන්න වෙනවා</t>
+  </si>
+  <si>
+    <t>Neg_0020</t>
+  </si>
+  <si>
+    <t>hariyata answer eka dena</t>
+  </si>
+  <si>
+    <t>හරියට answer එක දෙන්න</t>
+  </si>
+  <si>
+    <t>හරියට answer එක දෙන</t>
+  </si>
+  <si>
+    <t>Neg_0021</t>
+  </si>
+  <si>
+    <t>api Zoom class ekata join una</t>
+  </si>
+  <si>
+    <t>අපි Zoom class එකට join උනා</t>
+  </si>
+  <si>
+    <t>අපි Zoom class එකට join වුණා</t>
+  </si>
+  <si>
+    <t>Neg_0022</t>
+  </si>
+  <si>
+    <t>mama food order kala app eken</t>
+  </si>
+  <si>
+    <t>මම ආහාර order කළා app එකෙන්</t>
+  </si>
+  <si>
+    <t>මම food order කළා app එකෙන්</t>
+  </si>
+  <si>
+    <t>Neg_0023</t>
+  </si>
+  <si>
+    <t>electricity cut nisa mama laptop eke work karanna bari una</t>
+  </si>
+  <si>
+    <t>electricity cut නිසා මම laptop එකේ work කරන්න බැරි උනා</t>
+  </si>
+  <si>
+    <t>electricity cut නිසා මම laptop එකේ work කරන්න බැරි වුණා</t>
+  </si>
+  <si>
+    <t>Neg_0024</t>
+  </si>
+  <si>
+    <t>meeting eka postpone kala</t>
+  </si>
+  <si>
+    <t>රැස්වීම එක postpone කළා</t>
+  </si>
+  <si>
+    <t>meeting එක postpone කළා</t>
+  </si>
+  <si>
+    <t>Neg_0025</t>
+  </si>
+  <si>
+    <t>teacher kiwwa ASAP assignment eka denna kiyala</t>
+  </si>
+  <si>
+    <t>ගුරුවරයා කිව්වා ASAP assignment එක දෙන්න කියලා</t>
+  </si>
+  <si>
+    <t>teacher කිව්වා ASAP assignment එක දෙන්න කියලා</t>
+  </si>
+  <si>
+    <t>Neg_0026</t>
+  </si>
+  <si>
+    <t>mama Instagram post ekak upload kala</t>
+  </si>
+  <si>
+    <t>මම Instagram post එකක් උඩුගත කළා</t>
+  </si>
+  <si>
+    <t>මම Instagram post එකක් upload කළා</t>
+  </si>
+  <si>
+    <t>Neg_0027</t>
+  </si>
+  <si>
+    <t>salary delay nisa employees la stress wela inne</t>
+  </si>
+  <si>
+    <t>salary delay නිසා employees ලා ආතතිය වෙලා ඉන්නේ</t>
+  </si>
+  <si>
+    <t>salary delay නිසා employees ලා stress වෙලා ඉන්නේ</t>
+  </si>
+  <si>
+    <t>Neg_0028</t>
+  </si>
+  <si>
+    <t>api cricket match eka baluwa</t>
+  </si>
+  <si>
+    <t>අපි ක්‍රිකට් match එක බැලුවා</t>
+  </si>
+  <si>
+    <t>අපි cricket match එක බැලුවා</t>
+  </si>
+  <si>
+    <t>Neg_0029</t>
+  </si>
+  <si>
+    <t>Instagram post ekak damma</t>
+  </si>
+  <si>
+    <t>Instagram පෝස්ට් එකක් දැම්මා</t>
+  </si>
+  <si>
+    <t>Instagram post එකක් දැම්මා</t>
+  </si>
+  <si>
+    <t>Neg_0030</t>
+  </si>
+  <si>
+    <t>mama Google search kala information ganna</t>
+  </si>
+  <si>
+    <t>මම Google search කළා තොරතුරු ගන්න</t>
+  </si>
+  <si>
+    <t>මම Google search කළා information ගන්න</t>
+  </si>
+  <si>
+    <t>Neg_0031</t>
+  </si>
+  <si>
+    <t>traffic jam nisa office eka yanna godak late una</t>
+  </si>
+  <si>
+    <t>traffic jam නිසා office එක යන්න ගොඩක් late උනා</t>
+  </si>
+  <si>
+    <t>traffic jam නිසා office එක යන්න ගොඩක් late වුණා</t>
+  </si>
+  <si>
+    <t>Neg_0032</t>
+  </si>
+  <si>
+    <t>mama laptop eka restart kala</t>
+  </si>
+  <si>
+    <t>මම ලැප්ටොප් එක restart කළා</t>
+  </si>
+  <si>
+    <t>මම laptop එක restart කළා</t>
+  </si>
+  <si>
+    <t>Neg_0033</t>
+  </si>
+  <si>
+    <t>Facebook message ekak awa</t>
+  </si>
+  <si>
+    <t>Facebook පණිවිඩය එකක් ආවා</t>
+  </si>
+  <si>
+    <t>Facebook message එකක් ආවා</t>
+  </si>
+  <si>
+    <t>Neg_0034</t>
+  </si>
+  <si>
+    <t>mama payment eka online kala</t>
+  </si>
+  <si>
+    <t>මම ගෙවීම් එක online කළා</t>
+  </si>
+  <si>
+    <t>මම payment එක online කළා</t>
+  </si>
+  <si>
+    <t>Neg_0035</t>
+  </si>
+  <si>
+    <t>internet slow nisa zoom class eka properly attend karanna bari una</t>
+  </si>
+  <si>
+    <t>internet slow නිසා zoom class එක properly attend කරන්න බැරි උනා</t>
+  </si>
+  <si>
+    <t>internet slow නිසා zoom class එක properly attend කරන්න බැරි වුණා</t>
+  </si>
+  <si>
+    <t>Neg_0036</t>
+  </si>
+  <si>
+    <t>mama photo edit kala Photoshop use karala</t>
+  </si>
+  <si>
+    <t>මම photo edit කළා Photoshop භාවිතා  කරලා</t>
+  </si>
+  <si>
+    <t>මම photo edit කළා Photoshop use කරලා</t>
+  </si>
+  <si>
+    <t>Neg_0037</t>
+  </si>
+  <si>
+    <t>mama next week project eka complete karanawa</t>
+  </si>
+  <si>
+    <t>මම next week ව්‍යාපෘතිය එක complete කරනවා</t>
+  </si>
+  <si>
+    <t>මම next week project එක complete කරනවා</t>
+  </si>
+  <si>
+    <t>Neg_0038</t>
+  </si>
+  <si>
+    <t>mama email ekak send kala client ta</t>
+  </si>
+  <si>
+    <t>මම email එකක් send කළා සේවාදායකයා ට</t>
+  </si>
+  <si>
+    <t>මම email එකක් send කළා client ට</t>
+  </si>
+  <si>
+    <t>Neg_0039</t>
+  </si>
+  <si>
+    <t>power cut nisa mama assignment eka save karanna bari wela lost una</t>
+  </si>
+  <si>
+    <t>power cut නිසා assignment එක save කරන්න බැරි වෙලා lost උනා</t>
+  </si>
+  <si>
+    <t>power cut නිසා මම assignment එක save කරන්න බැරි වෙලා lost වුණා</t>
+  </si>
+  <si>
+    <t>Neg_0040</t>
+  </si>
+  <si>
+    <t>mama mobile data on kala</t>
+  </si>
+  <si>
+    <t>මම ජංගම data on කළා</t>
+  </si>
+  <si>
+    <t>මම mobile data on කළා</t>
+  </si>
+  <si>
+    <t>Neg_0041</t>
+  </si>
+  <si>
+    <t>system update ekak awa</t>
+  </si>
+  <si>
+    <t>system යාවත්කාලීන එකක් ආවා</t>
+  </si>
+  <si>
+    <t>system update එකක් ආවා</t>
+  </si>
+  <si>
+    <t>Neg_0042</t>
+  </si>
+  <si>
+    <t>mama Netflix eke movie baluwa</t>
+  </si>
+  <si>
+    <t>මම Netflix එකේ චිත්‍රපටිය බැලුවා</t>
+  </si>
+  <si>
+    <t>මම Netflix එකේ movie බැලුවා</t>
+  </si>
+  <si>
+    <t>Neg_0043</t>
+  </si>
+  <si>
+    <t>boss meeting eka cancel kala nisa employees la free wela inne</t>
+  </si>
+  <si>
+    <t>boss රැස්වීම එක cancel කළා නිසා employees ලා free වෙලා ඉන්නේ</t>
+  </si>
+  <si>
+    <t>boss meeting එක cancel කළා නිසා employees ලා free වෙලා ඉන්නේ</t>
+  </si>
+  <si>
+    <t>Neg_0044</t>
+  </si>
+  <si>
+    <t>mama alarm set kala morning</t>
+  </si>
+  <si>
+    <t>මම alarm set කළා උදේ</t>
+  </si>
+  <si>
+    <t>මම alarm set කළා morning</t>
+  </si>
+  <si>
+    <t>Neg_0045</t>
+  </si>
+  <si>
+    <t>mobile data off kala</t>
+  </si>
+  <si>
+    <t>mobile දත්ත off කළා</t>
+  </si>
+  <si>
+    <t>mobile data off කළා</t>
+  </si>
+  <si>
+    <t>Neg_0046</t>
+  </si>
+  <si>
+    <t>mama WiFi connect kala</t>
+  </si>
+  <si>
+    <t>මම WiFi සම්බන්ධ කළා</t>
+  </si>
+  <si>
+    <t>මම WiFi connect කළා</t>
+  </si>
+  <si>
+    <t>Neg_0047</t>
+  </si>
+  <si>
+    <t>rain nisa road  slippery wela accident risk wadi wela thiyenawa</t>
+  </si>
+  <si>
+    <t>rain නිසා මාර්ගය slippery වෙලා accident risk වැඩි වෙලා තියෙනවා</t>
+  </si>
+  <si>
+    <t>rain නිසා road slippery වෙලා accident risk වැඩි වෙලා තියෙනවා</t>
+  </si>
+  <si>
+    <t>Neg_0048</t>
+  </si>
+  <si>
+    <t>mama YouTube video ekak upload kala</t>
+  </si>
+  <si>
+    <t>මම YouTube video එකක් උඩුගත කළා</t>
+  </si>
+  <si>
+    <t>මම YouTube video එකක් upload කළා</t>
+  </si>
+  <si>
+    <t>Neg_0049</t>
+  </si>
+  <si>
+    <t>backup restore kala</t>
+  </si>
+  <si>
+    <t>backup යථා තත්ත්වයට පත් කිරීම කළා</t>
+  </si>
+  <si>
+    <t>backup restore කළා</t>
+  </si>
+  <si>
+    <t>Neg_0050</t>
+  </si>
+  <si>
+    <t>mama laptop charger eka connect kala</t>
+  </si>
+  <si>
+    <t>මම laptop චාජර් එක connect කළා</t>
+  </si>
+  <si>
+    <t>මම laptop charger එක connect කළා</t>
+  </si>
+  <si>
     <t>project deadline එක නිසා team එක pressure වෙලා ඉන්නේ</t>
   </si>
   <si>
-    <t>Neg_0015</t>
-  </si>
-  <si>
-    <t>mama phone eka use karala assignment eka complete kala</t>
-  </si>
-  <si>
-    <t>මම phone එක use කරලා assignment එක complete කළා</t>
-  </si>
-  <si>
-    <t>Neg_0016</t>
-  </si>
-  <si>
-    <t>oyage WiFi password mokakda</t>
-  </si>
-  <si>
-    <t>ඔයාගේ WiFi password මොකක්ද</t>
-  </si>
-  <si>
-    <t>Neg_0017</t>
-  </si>
-  <si>
-    <t>mama bus eke travel karanawa</t>
-  </si>
-  <si>
-    <t>මම bus එකේ travel කරනවා</t>
-  </si>
-  <si>
-    <t>Neg_0018</t>
-  </si>
-  <si>
-    <t>oyata update ekak thiyenawa</t>
-  </si>
-  <si>
-    <t>ඔයාට update එකක් තියෙනවා</t>
-  </si>
-  <si>
-    <t>Neg_0019</t>
-  </si>
-  <si>
-    <t>online class eka nisa mama home office eke inna wenawa</t>
-  </si>
-  <si>
-    <t>online class එක නිසා මම home office එකේ ඉන්න වෙනවා</t>
-  </si>
-  <si>
-    <t>Neg_0020</t>
-  </si>
-  <si>
-    <t>hariyata answer eka dena</t>
-  </si>
-  <si>
-    <t>හරියට answer එක දෙන්න</t>
-  </si>
-  <si>
-    <t>Neg_0021</t>
-  </si>
-  <si>
-    <t>api Zoom class ekata join una</t>
-  </si>
-  <si>
-    <t>අපි Zoom class එකට join උනා</t>
-  </si>
-  <si>
-    <t>Neg_0022</t>
-  </si>
-  <si>
-    <t>mama food order kala app eken</t>
-  </si>
-  <si>
-    <t>මම food order කළා app එකෙන්</t>
-  </si>
-  <si>
-    <t>Neg_0023</t>
-  </si>
-  <si>
-    <t>electricity cut nisa mama laptop eke work karanna bari una</t>
-  </si>
-  <si>
-    <t>electricity cut නිසා මම laptop එකේ work කරන්න බැරි උනා</t>
-  </si>
-  <si>
-    <t>Neg_0024</t>
-  </si>
-  <si>
-    <t>meeting eka postpone kala</t>
-  </si>
-  <si>
-    <t>meeting එක postpone කළා</t>
-  </si>
-  <si>
-    <t>Neg_0025</t>
-  </si>
-  <si>
-    <t>teacher kiwwa ASAP assignment eka denna kiyala</t>
-  </si>
-  <si>
-    <t>teacher කිව්වා ASAP assignment එක දෙන්න කියලා</t>
-  </si>
-  <si>
-    <t>Neg_0026</t>
-  </si>
-  <si>
-    <t>mama Instagram post ekak upload kala</t>
-  </si>
-  <si>
-    <t>මම Instagram post එකක් upload කළා</t>
-  </si>
-  <si>
-    <t>Neg_0027</t>
-  </si>
-  <si>
-    <t>salary delay nisa employees la stress wela inne</t>
-  </si>
-  <si>
-    <t>salary delay නිසා employees ලා stress වෙලා ඉන්නේ</t>
-  </si>
-  <si>
-    <t>Neg_0028</t>
-  </si>
-  <si>
-    <t>api cricket match eka baluwa</t>
-  </si>
-  <si>
-    <t>අපි cricket match එක බැලුවා</t>
-  </si>
-  <si>
-    <t>UI Error</t>
-  </si>
-  <si>
-    <t>Neg_0029</t>
-  </si>
-  <si>
-    <t>one</t>
-  </si>
-  <si>
-    <t>ඕන</t>
-  </si>
-  <si>
-    <t>Neg_0030</t>
-  </si>
-  <si>
-    <t>mama Google search kala information ganna</t>
-  </si>
-  <si>
-    <t>මම Google search කළා information ගන්න</t>
-  </si>
-  <si>
-    <t>ඕනේ</t>
-  </si>
-  <si>
-    <t>Neg_0031</t>
-  </si>
-  <si>
-    <t>traffic jam nisa office eka yanna godak late una</t>
-  </si>
-  <si>
-    <t>traffic jam නිසා office එක යන්න ගොඩක් late උනා</t>
-  </si>
-  <si>
-    <t>Neg_0032</t>
-  </si>
-  <si>
-    <t>mama laptop eka restart kala</t>
-  </si>
-  <si>
-    <t>මම laptop එක restart කළා</t>
-  </si>
-  <si>
-    <t>traffic jam නිසා office එක යන්න ගොඩක් late වුණා</t>
-  </si>
-  <si>
-    <t>Neg_0033</t>
-  </si>
-  <si>
-    <t>hari na</t>
-  </si>
-  <si>
-    <t>හරි නෑ</t>
-  </si>
-  <si>
-    <t>Neg_0034</t>
-  </si>
-  <si>
-    <t>mama payment eka online kala</t>
-  </si>
-  <si>
-    <t>මම payment එක online කළා</t>
-  </si>
-  <si>
-    <t>Neg_0035</t>
-  </si>
-  <si>
-    <t>internet slow nisa zoom class eka properly attend karanna bari una</t>
-  </si>
-  <si>
-    <t>internet slow නිසා zoom class එක properly attend කරන්න බැරි උනා</t>
-  </si>
-  <si>
-    <t>Neg_0036</t>
-  </si>
-  <si>
-    <t>mama photo edit kala Photoshop use karala</t>
-  </si>
-  <si>
-    <t>මම photo edit කළා Photoshop use කරලා</t>
-  </si>
-  <si>
-    <t>Neg_0037</t>
-  </si>
-  <si>
-    <t>mama next week project eka complete karanawa</t>
-  </si>
-  <si>
-    <t>මම next week project එක complete කරනවා</t>
-  </si>
-  <si>
-    <t>Neg_0038</t>
-  </si>
-  <si>
-    <t>mama email ekak send kala client ta</t>
-  </si>
-  <si>
-    <t>මම email එකක් send කළා client ට</t>
-  </si>
-  <si>
-    <t>Neg_0039</t>
-  </si>
-  <si>
-    <t>power cut nisa mama assignment eka save karanna bari wela lost una</t>
-  </si>
-  <si>
-    <t>power cut නිසා assignment එක save කරන්න බැරි වෙලා lost උනා</t>
-  </si>
-  <si>
-    <t>Neg_0040</t>
-  </si>
-  <si>
-    <t>mama mobile data on kala</t>
-  </si>
-  <si>
-    <t>මම mobile data on කළා</t>
-  </si>
-  <si>
-    <t>Neg_0041</t>
-  </si>
-  <si>
-    <t>system update ekak awa</t>
-  </si>
-  <si>
-    <t>system update එකක් ආවා</t>
-  </si>
-  <si>
-    <t>Neg_0042</t>
-  </si>
-  <si>
-    <t>mama Netflix eke movie baluwa</t>
-  </si>
-  <si>
-    <t>මම Netflix එකේ movie බැලුවා</t>
-  </si>
-  <si>
-    <t>Neg_0043</t>
-  </si>
-  <si>
-    <t>boss meeting eka cancel kala nisa employees la free wela inne</t>
-  </si>
-  <si>
-    <t>boss meeting එක cancel කළා නිසා employees ලා free වෙලා ඉන්නේ</t>
-  </si>
-  <si>
-    <t>Neg_0044</t>
-  </si>
-  <si>
-    <t>mama alarm set kala morning</t>
-  </si>
-  <si>
-    <t>මම alarm set කළා morning</t>
-  </si>
-  <si>
-    <t>Neg_0045</t>
-  </si>
-  <si>
-    <t>mobile data off kala</t>
-  </si>
-  <si>
-    <t>mobile data off කළා</t>
-  </si>
-  <si>
-    <t>Neg_0046</t>
-  </si>
-  <si>
-    <t>mama WiFi connect kala</t>
-  </si>
-  <si>
-    <t>මම WiFi connect කළා</t>
-  </si>
-  <si>
-    <t>Neg_0047</t>
-  </si>
-  <si>
-    <t>rain nisa road eka slippery wela accident risk wadi wela thiyenawa</t>
-  </si>
-  <si>
-    <t>rain නිසා road එක slippery වෙලා accident risk වැඩි වෙලා තියෙනවා</t>
-  </si>
-  <si>
-    <t>Neg_0048</t>
-  </si>
-  <si>
-    <t>mama YouTube video ekak upload kala</t>
-  </si>
-  <si>
-    <t>මම YouTube video එකක් upload කළා</t>
-  </si>
-  <si>
-    <t>Neg_0049</t>
-  </si>
-  <si>
-    <t>backup restore kala</t>
-  </si>
-  <si>
-    <t>backup restore කළා</t>
-  </si>
-  <si>
-    <t>Neg_0050</t>
-  </si>
-  <si>
-    <t>mama laptop charger eka connect kala</t>
-  </si>
-  <si>
-    <t>මම laptop charger එක connect කළා</t>
-  </si>
-  <si>
-    <t>salary delay නිසා employees ලා stress වෙල ඉන්නේ</t>
+    <t>Singlish Input Types Covered</t>
+  </si>
+  <si>
+    <t>Evidence or Rationale (Ordered)</t>
+  </si>
+  <si>
+    <t>Long sentence with English mix</t>
+  </si>
+  <si>
+    <t>"office eke වැඩ ගොඩක් තිබුනු නිසා lunch එක ගොඩාක් late උනා" – Sinhala + English mixed long sentence</t>
+  </si>
+  <si>
+    <t>Simple command</t>
+  </si>
+  <si>
+    <t>"මට පොත දෙන්න" – direct command/request</t>
+  </si>
+  <si>
+    <t>Mixed sentence (Sinhala + English nouns)</t>
+  </si>
+  <si>
+    <t>"මම අද dinner ගන්න hotel එකට ගියා" – English nouns inside Sinhala sentence</t>
+  </si>
+  <si>
+    <t>Technical + English terms</t>
+  </si>
+  <si>
+    <t>"අපි meeting එක start කරන්නේ 10ට" – meeting, start</t>
+  </si>
+  <si>
+    <t>"මම file එක upload කරලා submit කළා" – upload, submit</t>
+  </si>
+  <si>
+    <t>Polite request</t>
+  </si>
+  <si>
+    <t>"ඔයා call එකක් දෙන්න පුළුවන්ද" – polite question form</t>
+  </si>
+  <si>
+    <t>Mixed formal/informal spoken style</t>
+  </si>
+  <si>
+    <t>"ඔෆිස් එකේ meeting එකක් තිබුණා" – workplace + casual Sinhala</t>
+  </si>
+  <si>
+    <t>Need / requirement expression</t>
+  </si>
+  <si>
+    <t>"මට අද leave එකක් ඕන" – necessity expression</t>
+  </si>
+  <si>
+    <t>Informal spoken style</t>
+  </si>
+  <si>
+    <t>"අපි game එක play කළා" – casual spoken mix</t>
+  </si>
+  <si>
+    <t>"හරියට plan එක තිබ්බා" – casual planning expression</t>
+  </si>
+  <si>
+    <t>Repetition / emphasis</t>
+  </si>
+  <si>
+    <t>"ඔෆිස් එකේ වැඩ ගොඩක් තිබුනා නිසා lunch එක late උනා" – idea repeated with variation</t>
+  </si>
+  <si>
+    <t>Routine + tech mix</t>
+  </si>
+  <si>
+    <t>"මම උදේ wake up වෙලා zoom meeting එකට join උනා"</t>
+  </si>
+  <si>
+    <t>"exam එක නිසා මම රෑ whole night study කළා" – emphasis on intensity</t>
+  </si>
+  <si>
+    <t>Work pressure context</t>
+  </si>
+  <si>
+    <t>"project deadline එක නිසා team එක pressure වෙලා ඉන්නේ"</t>
+  </si>
+  <si>
+    <t>Device usage</t>
+  </si>
+  <si>
+    <t>"මම phone එක use කරලා assignment එක complete කළා"</t>
+  </si>
+  <si>
+    <t>Question form</t>
+  </si>
+  <si>
+    <t>"ඔයාගේ WiFi password මොකක්ද" – WH question</t>
+  </si>
+  <si>
+    <t>Travel context</t>
+  </si>
+  <si>
+    <t>"මම bus එකේ travel කරනවා"</t>
+  </si>
+  <si>
+    <t>Information update</t>
+  </si>
+  <si>
+    <t>"ඔයාට update එකක් තියෙනවා"</t>
+  </si>
+  <si>
+    <t>Hybrid work context</t>
+  </si>
+  <si>
+    <t>"online class එක නිසා මම home office එකේ ඉන්න වෙනවා"</t>
+  </si>
+  <si>
+    <t>"හරියට answer එක දෙන්න" – instruction</t>
+  </si>
+  <si>
+    <t>Platform/app usage</t>
+  </si>
+  <si>
+    <t>"අපි Zoom class එකට join උනා"</t>
+  </si>
+  <si>
+    <t>App-based action</t>
+  </si>
+  <si>
+    <t>"මම food order කළා app එකෙන්"</t>
+  </si>
+  <si>
+    <t>Problem situation</t>
+  </si>
+  <si>
+    <t>"electricity cut නිසා මම laptop එකේ work කරන්න බැරි උනා"</t>
+  </si>
+  <si>
+    <t>Scheduling change</t>
+  </si>
+  <si>
+    <t>"meeting එක postpone කළා"</t>
+  </si>
+  <si>
+    <t>Abbreviation / official term</t>
+  </si>
+  <si>
+    <t>"teacher කිව්වා ASAP assignment එක දෙන්න කියලා"</t>
+  </si>
+  <si>
+    <t>Social media action</t>
+  </si>
+  <si>
+    <t>"මම Instagram post එකක් upload කළා"</t>
+  </si>
+  <si>
+    <t>Workplace stress context</t>
+  </si>
+  <si>
+    <t>"salary delay නිසා employees ලා stress වෙල ඉන්නේ"</t>
+  </si>
+  <si>
+    <t>Entertainment context</t>
+  </si>
+  <si>
+    <t>"අපි cricket match එක බැලුවා"</t>
+  </si>
+  <si>
+    <t>Single-word informal</t>
+  </si>
+  <si>
+    <t>"ඕන" – minimal response</t>
+  </si>
+  <si>
+    <t>Search action</t>
+  </si>
+  <si>
+    <t>"මම Google search කළා information ගන්න"</t>
+  </si>
+  <si>
+    <t>Real-life + English mix</t>
+  </si>
+  <si>
+    <t>"traffic jam නිසා office එක යන්න ගොඩක් late උනා"</t>
+  </si>
+  <si>
+    <t>Device control</t>
+  </si>
+  <si>
+    <t>"මම laptop එක restart කළා"</t>
+  </si>
+  <si>
+    <t>"හරි නෑ" – casual negative response</t>
+  </si>
+  <si>
+    <t>Online transaction</t>
+  </si>
+  <si>
+    <t>"මම payment එක online කළා"</t>
+  </si>
+  <si>
+    <t>Network issue context</t>
+  </si>
+  <si>
+    <t>"internet slow නිසා zoom class එක properly attend කරන්න බැරි උනා"</t>
+  </si>
+  <si>
+    <t>Software usage</t>
+  </si>
+  <si>
+    <t>"මම photo edit කළා Photoshop use කරලා"</t>
+  </si>
+  <si>
+    <t>Future plan</t>
+  </si>
+  <si>
+    <t>"මම next week project එක complete කරනවා"</t>
+  </si>
+  <si>
+    <t>Communication action</t>
+  </si>
+  <si>
+    <t>"මම email එකක් send කළා client ට"</t>
+  </si>
+  <si>
+    <t>Data loss scenario</t>
+  </si>
+  <si>
+    <t>"power cut නිසා assignment එක save කරන්න බැරි වෙලා lost උනා"</t>
+  </si>
+  <si>
+    <t>Mobile setting</t>
+  </si>
+  <si>
+    <t>"මම mobile data on කළා"</t>
+  </si>
+  <si>
+    <t>System notification</t>
+  </si>
+  <si>
+    <t>"system update එකක් ආවා"</t>
+  </si>
+  <si>
+    <t>Streaming platform usage</t>
+  </si>
+  <si>
+    <t>"මම Netflix එකේ movie බැලුවා"</t>
+  </si>
+  <si>
+    <t>Workplace situation</t>
+  </si>
+  <si>
+    <t>"boss meeting එක cancel කළා නිසා employees ලා free වෙලා ඉන්නේ"</t>
+  </si>
+  <si>
+    <t>Daily routine tech</t>
+  </si>
+  <si>
+    <t>"මම alarm set කළා morning"</t>
+  </si>
+  <si>
+    <t>Toggle action</t>
+  </si>
+  <si>
+    <t>"mobile data off කළා"</t>
+  </si>
+  <si>
+    <t>Connectivity</t>
+  </si>
+  <si>
+    <t>"මම WiFi connect කළා"</t>
+  </si>
+  <si>
+    <t>Environmental + risk context</t>
+  </si>
+  <si>
+    <t>"rain නිසා road එක slippery වෙලා accident risk වැඩි වෙලා තියෙනවා"</t>
+  </si>
+  <si>
+    <t>Content creation</t>
+  </si>
+  <si>
+    <t>"මම YouTube video එකක් upload කළා"</t>
+  </si>
+  <si>
+    <t>System recovery</t>
+  </si>
+  <si>
+    <t>"backup restore කළා"</t>
+  </si>
+  <si>
+    <t>Hardware usage</t>
+  </si>
+  <si>
+    <t>"මම laptop charger එක connect කළා"</t>
   </si>
 </sst>
 </file>
@@ -897,19 +1326,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" customWidth="1"/>
-    <col min="3" max="3" width="42.33203125" customWidth="1"/>
-    <col min="4" max="4" width="53.6640625" customWidth="1"/>
-    <col min="5" max="5" width="17.77734375" customWidth="1"/>
-    <col min="6" max="6" width="25.21875" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" customWidth="1"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="6.21875" customWidth="1"/>
+    <col min="3" max="3" width="47.33203125" customWidth="1"/>
+    <col min="4" max="4" width="48.88671875" customWidth="1"/>
+    <col min="5" max="5" width="39.88671875" customWidth="1"/>
+    <col min="6" max="6" width="7.109375" customWidth="1"/>
+    <col min="7" max="7" width="36.44140625" customWidth="1"/>
+    <col min="8" max="8" width="33.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -928,9 +1358,14 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G1" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -943,958 +1378,1292 @@
       <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2"/>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="F2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="F3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="2"/>
+        <v>24</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="F5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="2"/>
+        <v>28</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="F6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="F7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="F8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="F9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="F10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="2"/>
+        <v>48</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="F11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="F12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="2"/>
+        <v>56</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="F13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="2"/>
+        <v>60</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="F14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="F15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" s="2"/>
+        <v>67</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="F16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E17" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>72</v>
+      </c>
       <c r="F17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="F18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>80</v>
+      </c>
       <c r="F19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E20" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="F20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E21" s="2"/>
+        <v>87</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="F21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E22" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="F22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E23" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>96</v>
+      </c>
       <c r="F23" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E24" s="2"/>
+        <v>99</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="F24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E25" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>104</v>
+      </c>
       <c r="F25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E26" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="F26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E27" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>112</v>
+      </c>
       <c r="F27" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>163</v>
+        <v>115</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E29" s="2"/>
+        <v>119</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>120</v>
+      </c>
       <c r="F29" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" s="2"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" s="2"/>
-    </row>
-    <row r="34" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" s="2"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G35" s="2"/>
-    </row>
-    <row r="36" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E36" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="F36" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G36" s="2"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E37" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>152</v>
+      </c>
       <c r="F37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G37" s="2"/>
-    </row>
-    <row r="38" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>122</v>
+        <v>154</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G38" s="2"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E39" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>160</v>
+      </c>
       <c r="F39" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G39" s="2"/>
-    </row>
-    <row r="40" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E40" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>164</v>
+      </c>
       <c r="F40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G40" s="2"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E41" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>168</v>
+      </c>
       <c r="F41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G41" s="2"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>133</v>
+        <v>169</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E42" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>172</v>
+      </c>
       <c r="F42" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G42" s="2"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E43" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="F43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G43" s="2"/>
-    </row>
-    <row r="44" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E44" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>180</v>
+      </c>
       <c r="F44" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G44" s="2"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>142</v>
+        <v>181</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>143</v>
+        <v>182</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E45" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>184</v>
+      </c>
       <c r="F45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G45" s="2"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>145</v>
+        <v>185</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>146</v>
+        <v>186</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E46" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>188</v>
+      </c>
       <c r="F46" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G46" s="2"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>148</v>
+        <v>189</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>149</v>
+        <v>190</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E47" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>192</v>
+      </c>
       <c r="F47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G47" s="2"/>
-    </row>
-    <row r="48" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E48" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>196</v>
+      </c>
       <c r="F48" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G48" s="2"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>154</v>
+        <v>197</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>155</v>
+        <v>198</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="E49" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>200</v>
+      </c>
       <c r="F49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G49" s="2"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>157</v>
+        <v>201</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>158</v>
+        <v>202</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E50" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>204</v>
+      </c>
       <c r="F50" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G50" s="2"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>160</v>
+        <v>205</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>161</v>
+        <v>206</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E51" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>208</v>
+      </c>
       <c r="F51" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G51" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>306</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
